--- a/globallbz1_p_ttl_16.xlsx
+++ b/globallbz1_p_ttl_16.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,52 +619,124 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>TTL</t>
+          <t>min_hop_time</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Average distance</t>
+          <t>min_hop_length</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>min_hop_hops</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>best_time</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>best_length</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>best_hops</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>worst_time</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>worst_length</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>worst_hops</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>average_distance</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ttl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B2" t="n">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="C2" t="n">
         <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>5060</v>
+        <v>5052</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F2" t="n">
-        <v>192.8421052631579</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H2" t="n">
-        <v>125.75</v>
+        <v>143</v>
       </c>
       <c r="I2" t="n">
-        <v>122</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="J2" t="n">
+        <v>244</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1416.206542346071</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>330</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1833.348481093416</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>171.5453638279912</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
         <v>30000</v>
@@ -673,29 +745,56 @@
         <v>5056</v>
       </c>
       <c r="E3" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="F3" t="n">
-        <v>197.3</v>
+        <v>234.75</v>
       </c>
       <c r="G3" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="H3" t="n">
-        <v>159.25</v>
+        <v>127</v>
       </c>
       <c r="I3" t="n">
-        <v>154</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="J3" t="n">
+        <v>245</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1591.578626228542</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>290</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1903.809938511102</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>168.1877157650203</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
         <v>30000</v>
@@ -704,60 +803,114 @@
         <v>5056</v>
       </c>
       <c r="E4" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>174.4</v>
+        <v>177.9166666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
-        <v>142.5</v>
+        <v>126</v>
       </c>
       <c r="I4" t="n">
-        <v>139</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="J4" t="n">
+        <v>213</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1556.2860407945</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>273</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1993.958431334087</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>173.86227100766843</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C5" t="n">
         <v>30000</v>
       </c>
       <c r="D5" t="n">
-        <v>5064</v>
+        <v>5056</v>
       </c>
       <c r="E5" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>193.0714285714286</v>
+        <v>176.8</v>
       </c>
       <c r="G5" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="I5" t="n">
-        <v>151</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="J5" t="n">
+        <v>170</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1562.786033474744</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>223</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2098.495084076439</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>168.0104616717245</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B6" t="n">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="C6" t="n">
         <v>30000</v>
@@ -766,91 +919,172 @@
         <v>5056</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F6" t="n">
-        <v>185.4444444444445</v>
+        <v>141.3333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
-        <v>137</v>
+        <v>141.3333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>136</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="J6" t="n">
+        <v>138</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1668.731540647929</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>247</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1712.487711011747</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>168.81118190359805</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
         <v>30000</v>
       </c>
       <c r="D7" t="n">
-        <v>5052</v>
+        <v>5060</v>
       </c>
       <c r="E7" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
-        <v>239</v>
+        <v>168.8</v>
       </c>
       <c r="G7" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H7" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="I7" t="n">
-        <v>113</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="J7" t="n">
+        <v>132</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1846.562458754093</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>291</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2201.02132764055</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>168.5794448850079</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
         <v>30000</v>
       </c>
       <c r="D8" t="n">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>149.7432432432433</v>
+        <v>205.6666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="H8" t="n">
-        <v>113.2</v>
+        <v>134.7857142857143</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="J8" t="n">
+        <v>206</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1495.978962995963</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>244</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1669.802971888396</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>164.81289404905172</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
         <v>30000</v>
@@ -859,29 +1093,56 @@
         <v>5056</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="F9" t="n">
-        <v>140.3846153846154</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="H9" t="n">
-        <v>130.5</v>
+        <v>169</v>
       </c>
       <c r="I9" t="n">
-        <v>127</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="J9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1534.837053883674</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>251</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2057.031454643266</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>171.7524100796294</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C10" t="n">
         <v>30000</v>
@@ -890,60 +1151,114 @@
         <v>5056</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="F10" t="n">
-        <v>172.6666666666667</v>
+        <v>170.3333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="H10" t="n">
-        <v>114.6666666666667</v>
+        <v>170.3333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>114</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="J10" t="n">
+        <v>167</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1434.808685612507</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>227</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2326.951029744161</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>160.03196063918867</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C11" t="n">
         <v>30000</v>
       </c>
       <c r="D11" t="n">
-        <v>5052</v>
+        <v>5056</v>
       </c>
       <c r="E11" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>212</v>
+        <v>201.75</v>
       </c>
       <c r="G11" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="H11" t="n">
-        <v>139</v>
+        <v>123.2</v>
       </c>
       <c r="I11" t="n">
-        <v>144</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="J11" t="n">
+        <v>217</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1664.808886593527</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>273</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1886.496186485351</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>170.8001698685842</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C12" t="n">
         <v>30000</v>
@@ -952,153 +1267,288 @@
         <v>5056</v>
       </c>
       <c r="E12" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>187.8205128205128</v>
+        <v>153.016393442623</v>
       </c>
       <c r="G12" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H12" t="n">
-        <v>111.6666666666667</v>
+        <v>111.5</v>
       </c>
       <c r="I12" t="n">
-        <v>111</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="J12" t="n">
+        <v>153</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1737.715902816122</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>259</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2111.935845023813</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>169.91732269944873</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C13" t="n">
         <v>30000</v>
       </c>
       <c r="D13" t="n">
-        <v>5056</v>
+        <v>5052</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>182.0227272727273</v>
+        <v>223</v>
       </c>
       <c r="G13" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="H13" t="n">
-        <v>114</v>
+        <v>149.5</v>
       </c>
       <c r="I13" t="n">
-        <v>111</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="J13" t="n">
+        <v>223</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1383.555956921019</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>321</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2393.92864674637</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>164.32618469965473</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C14" t="n">
         <v>30000</v>
       </c>
       <c r="D14" t="n">
-        <v>5052</v>
+        <v>5056</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>133</v>
+        <v>146.2222222222222</v>
       </c>
       <c r="G14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I14" t="n">
-        <v>109</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>113</v>
+      </c>
+      <c r="J14" t="n">
+        <v>211</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1594.536683554159</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2203.806193124522</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>166.8327073544929</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C15" t="n">
         <v>30000</v>
       </c>
       <c r="D15" t="n">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
-        <v>182.8</v>
+        <v>231.3333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="H15" t="n">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="I15" t="n">
-        <v>118</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="J15" t="n">
+        <v>262</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1346.502507348086</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>293</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1903.333015940501</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>164.02430931664983</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C16" t="n">
         <v>30000</v>
       </c>
       <c r="D16" t="n">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
-        <v>165.1698113207547</v>
+        <v>225.3333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H16" t="n">
-        <v>108</v>
+        <v>126.8333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>108</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>224</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1650.896083070469</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>273</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1670.2169856155</v>
+      </c>
+      <c r="O16" t="n">
+        <v>9</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>167.2461878425074</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B17" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C17" t="n">
         <v>30000</v>
@@ -1107,60 +1557,114 @@
         <v>5052</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F17" t="n">
-        <v>202</v>
+        <v>226.25</v>
       </c>
       <c r="G17" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H17" t="n">
-        <v>130.5</v>
+        <v>113.5</v>
       </c>
       <c r="I17" t="n">
-        <v>124</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="J17" t="n">
+        <v>212</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1455.761177970195</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>286</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1724.447438912231</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>162.84386443229494</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B18" t="n">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="C18" t="n">
         <v>30000</v>
       </c>
       <c r="D18" t="n">
-        <v>5064</v>
+        <v>5056</v>
       </c>
       <c r="E18" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>139.7882352941176</v>
+        <v>214.2083333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H18" t="n">
-        <v>127.1666666666667</v>
+        <v>141.1666666666667</v>
       </c>
       <c r="I18" t="n">
-        <v>125</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="J18" t="n">
+        <v>200</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1664.603906001007</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>290</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1806.380303847196</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>165.66492819107478</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B19" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C19" t="n">
         <v>30000</v>
@@ -1169,84 +1673,165 @@
         <v>5052</v>
       </c>
       <c r="E19" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="F19" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="H19" t="n">
-        <v>167.5</v>
+        <v>144</v>
       </c>
       <c r="I19" t="n">
-        <v>158</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+        <v>141</v>
+      </c>
+      <c r="J19" t="n">
+        <v>147</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1563.615510895055</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>289</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2157.714058230691</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>169.72543814250696</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C20" t="n">
         <v>30000</v>
       </c>
       <c r="D20" t="n">
-        <v>5056</v>
+        <v>5060</v>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="F20" t="n">
-        <v>146</v>
+        <v>226.85</v>
       </c>
       <c r="G20" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H20" t="n">
-        <v>125.25</v>
+        <v>160</v>
       </c>
       <c r="I20" t="n">
-        <v>120</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="J20" t="n">
+        <v>214</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1935.720304190436</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>291</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2058.646811275272</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>164.73082836364054</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C21" t="n">
         <v>30000</v>
       </c>
       <c r="D21" t="n">
-        <v>5052</v>
+        <v>5060</v>
       </c>
       <c r="E21" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="F21" t="n">
-        <v>197.8333333333333</v>
+        <v>206.8</v>
       </c>
       <c r="G21" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H21" t="n">
-        <v>128</v>
+        <v>115.25</v>
       </c>
       <c r="I21" t="n">
-        <v>128</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="J21" t="n">
+        <v>234</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1575.761199799247</v>
+      </c>
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="n">
+        <v>271</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2160.230200667124</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>162.90179875321397</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
